--- a/salidas/CONSOLIDADO.xlsx
+++ b/salidas/CONSOLIDADO.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P17"/>
+  <dimension ref="A1:U17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,45 +454,70 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>correo_electronico</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>foto_1_path</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>foto_2_path</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>foto_1_kb</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>foto_2_kb</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
           <t>calle</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>numero</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>manzana_inegi</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>manzana</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>lote</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>curp</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>coordenadas_gps</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>direccion_base</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>fecha_captura</t>
         </is>
@@ -534,39 +559,44 @@
           <t>5555555555</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
         <is>
           <t>ETA</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>11453001</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>XXXXXXXXXX</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
+          <t>11453001</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>XXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr">
+        <is>
           <t>Calle: calle eta mz 2 num int: lote18 Col: Lomas de Becerra S1</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>2026-03-05T20:56:26.658Z</t>
         </is>
@@ -608,39 +638,44 @@
           <t>5555555555</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
         <is>
           <t>ETA</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>11453001</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>XXXXXXXXXXXXX</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
+          <t>11453001</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>XXXXXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr">
+        <is>
           <t>Calle: calle eta mz 1 num int: lt 2 Col: Lomas de Becerra S1</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>2026-03-05T20:57:40.937Z</t>
         </is>
@@ -684,37 +719,62 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>consueloenmes@gmail.com</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>fotos/ines_pacheco/device-z9p72n/1773076555958-28bsx_1.jpg</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fotos/ines_pacheco/device-z9p72n/1773076555958-28bsx_2.jpg</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
           <t>Morelos</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>12 - 9</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>11453047</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
         <is>
           <t>Lhdi6doyf7</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>19.389539,-99.195183</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Calle: morelos 12 num int: 9 Col: Lomas de Becerra S1</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>2026-03-09T17:15:55.959Z</t>
         </is>
@@ -758,37 +818,62 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
+          <t>delvallepau@hotmail.com</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>fotos/ines_pacheco/device-z9p72n/1773076708181-luodg_1.jpg</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fotos/ines_pacheco/device-z9p72n/1773076708181-luodg_2.jpg</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
           <t>Etta</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>11453005</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
         <is>
           <t>Kasodjdnd</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>19.389562,-99.195197</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Calle: ETTA 6 num int: no tiene Col: Lomas de Becerra S1</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>2026-03-09T17:18:28.181Z</t>
         </is>
@@ -832,41 +917,66 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
+          <t>emelia.hernandez@gmail.com</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>fotos/maria_de_los_angeles_basurto/device-kv02so/1773076721792-fhb42_1.jpg</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fotos/maria_de_los_angeles_basurto/device-kv02so/1773076721792-fhb42_2.jpg</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
           <t>Eta</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
         <is>
           <t>11453001</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>Emhg230578mdfrnsoo</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>19.389592,-99.195213</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Calle: calle eta mz 1 num int: lt 2 Col: Lomas de Becerra S1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>2026-03-09T17:18:41.808Z</t>
         </is>
@@ -910,37 +1020,62 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
+          <t>lulu50@gmail.com</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>fotos/ines_pacheco/device-z9p72n/1773076886443-evkzq_1.jpg</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fotos/ines_pacheco/device-z9p72n/1773076886443-evkzq_2.jpg</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
           <t>Etta</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
         <is>
           <t>11453005</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
         <is>
           <t>Sosjdidkmflfll</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>19.389573,-99.195197</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Calle: Etta mz. 2 num int: lote 3 Col: Lomas de Becerra S1</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>2026-03-09T17:22:41.521Z</t>
         </is>
@@ -984,41 +1119,66 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
+          <t>mariablassil@gmail.com</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>fotos/maria_de_los_angeles_basurto/device-kv02so/1773076963536-avvic_1.jpg</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fotos/maria_de_los_angeles_basurto/device-kv02so/1773076963536-avvic_2.jpg</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
           <t>Principal</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>10385023</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Int. 1</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>Mahtmdf271198hsrn05</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>19.389588,-99.195220</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Calle: principal  8 num int: 1 Col: Lomas de Becerra S1</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>2026-03-09T17:22:43.569Z</t>
         </is>
@@ -1062,37 +1222,62 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
+          <t>malugo@aol.com</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>fotos/ines_pacheco/device-z9p72n/1773077122877-ihvud_1.jpg</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fotos/ines_pacheco/device-z9p72n/1773077122877-ihvud_2.jpg</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
           <t>Andador 2</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>10385023</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
         <is>
           <t>KHDIYDOYFIYZITZIT</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>19.389546,-99.195200</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Calle: andador 2  4 num int:  Col: Lomas de Becerra S1</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>2026-03-09T17:25:22.878Z</t>
         </is>
@@ -1136,41 +1321,66 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
+          <t>alirile@gmail.com</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>fotos/maria_de_los_angeles_basurto/device-kv02so/1773077186211-w4ool_1.jpg</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fotos/maria_de_los_angeles_basurto/device-kv02so/1773077186211-w4ool_2.jpg</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
           <t>Capa</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>11453001</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>Int. 3</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
         <is>
           <t>Rila230467mhgsrb07</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>19.389594,-99.195209</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Calle: calle capa 3 num int: 3 Col: Lomas de Becerra S1</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>2026-03-09T17:26:26.223Z</t>
         </is>
@@ -1214,37 +1424,62 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
+          <t>marcast@outlook.com</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>fotos/ines_pacheco/device-z9p72n/1773077281530-13zzd_1.jpg</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fotos/ines_pacheco/device-z9p72n/1773077281530-13zzd_2.jpg</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
           <t>Morelos 6A</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>11453047</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
         <is>
           <t>IGC96G96GUPGUP</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>19.389559,-99.195191</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Calle: calle  morelos  6A num int: 28 Col: Lomas de Becerra S1</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>2026-03-09T17:28:01.530Z</t>
         </is>
@@ -1288,41 +1523,66 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
+          <t>mari.lema@gmail.com</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>fotos/maria_de_los_angeles_basurto/device-kv02so/1773077369199-irztr_1.jpg</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fotos/maria_de_los_angeles_basurto/device-kv02so/1773077369199-irztr_2.jpg</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
           <t>Eta</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
         <is>
           <t>11453001</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Int. 18</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>Lehm431020HHGRRR15</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>19.389592,-99.195223</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Calle: calle eta mz 2 num int: lote18 Col: Lomas de Becerra S1</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>2026-03-09T17:29:29.213Z</t>
         </is>
@@ -1366,41 +1626,66 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
+          <t>malenu@gmail.com</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>fotos/maria_de_los_angeles_basurto/device-kv02so/1773077506448-35or9_1.jpg</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fotos/maria_de_los_angeles_basurto/device-kv02so/1773077506448-35or9_2.jpg</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
           <t>Omicron</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
         <is>
           <t>11453024</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>Numl120789mdfgrsn01</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>19.389574,-99.195211</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Calle: OMICRON MZ6 num int: LT10 Col: Lomas de Becerra S1</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>2026-03-09T17:31:46.488Z</t>
         </is>
@@ -1444,37 +1729,62 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
+          <t>sanchezcris@gmail.com</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>fotos/ines_pacheco/device-z9p72n/1773077818445-o9t3x_1.jpg</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fotos/ines_pacheco/device-z9p72n/1773077818445-o9t3x_2.jpg</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
           <t>Omicron</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>2 - 2</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>11453024</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
         <is>
           <t>JADIGLGLSMSK</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>19.389574,-99.195189</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>Calle: omicron 2 num int: 2 Col: Lomas de Becerra S1</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>2026-03-09T17:36:58.445Z</t>
         </is>
@@ -1518,37 +1828,62 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
+          <t>luciestmart@hotmail.com</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>fotos/ines_pacheco/device-z9p72n/1773077939013-u8kge_1.jpg</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fotos/ines_pacheco/device-z9p72n/1773077939013-u8kge_2.jpg</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
           <t>Antigua via la venta</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>71</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>11453047</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
         <is>
           <t>JAQKJQIWBSIHI</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>19.389554,-99.195185</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>Calle: antigua vía laventa 71 num int: 0 Col: Lomas de Becerra S1</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>2026-03-09T17:38:59.014Z</t>
         </is>
@@ -1592,33 +1927,58 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
+          <t>demmihy@gmail.com</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>fotos/maria_de_los_angeles_basurto/device-kv02so/1773078212848-kpdln_1.jpg</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fotos/maria_de_los_angeles_basurto/device-kv02so/1773078212848-kpdln_2.jpg</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
           <t>Cda. Tehuatepec</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>Maum650918mhgrt00</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>19.389574,-99.195209</t>
-        </is>
-      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Maum650918mhgrt00</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>19.389574,-99.195209</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr">
         <is>
           <t>2026-03-09T17:43:32.892Z</t>
         </is>
@@ -1662,41 +2022,66 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
+          <t>gaboga45@gmail.com</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>fotos/maria_de_los_angeles_basurto/device-kv02so/1773078376023-8v971_1.jpg</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fotos/maria_de_los_angeles_basurto/device-kv02so/1773078376023-8v971_2.jpg</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
           <t>Eta</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
         <is>
           <t>11453001</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>Bogg831203mdfhgrbm07</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>19.389585,-99.195207</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Calle: calle eta me 1 lote 9 num int:  Col: Lomas de Becerra S1</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>2026-03-09T17:46:16.066Z</t>
         </is>

--- a/salidas/CONSOLIDADO.xlsx
+++ b/salidas/CONSOLIDADO.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U17"/>
+  <dimension ref="A1:Y17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,55 +469,75 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
+          <t>foto_3_path</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>foto_1_kb</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>foto_2_kb</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>foto_3_kb</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
         <is>
           <t>calle</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>numero</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>manzana_inegi</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>manzana</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>lote</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>curp</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>colonia</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>codigo_postal</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
         <is>
           <t>coordenadas_gps</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>direccion_base</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>fecha_captura</t>
         </is>
@@ -564,39 +584,43 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>ETA</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
+          <t>ETA</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>11453001</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>XXXXXXXXXX</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
         <is>
           <t>Calle: calle eta mz 2 num int: lote18 Col: Lomas de Becerra S1</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>2026-03-05T20:56:26.658Z</t>
         </is>
@@ -643,39 +667,43 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>ETA</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
+          <t>ETA</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>11453001</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>XXXXXXXXXXXXX</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
         <is>
           <t>Calle: calle eta mz 1 num int: lt 2 Col: Lomas de Becerra S1</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>2026-03-05T20:57:40.937Z</t>
         </is>
@@ -732,49 +760,53 @@
           <t>fotos/ines_pacheco/device-z9p72n/1773076555958-28bsx_2.jpg</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
         <is>
           <t>Morelos</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>12 - 9</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>11453047</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr">
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr">
         <is>
           <t>Lhdi6doyf7</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr">
         <is>
           <t>19.389539,-99.195183</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>Calle: morelos 12 num int: 9 Col: Lomas de Becerra S1</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>2026-03-09T17:15:55.959Z</t>
         </is>
@@ -831,49 +863,53 @@
           <t>fotos/ines_pacheco/device-z9p72n/1773076708181-luodg_2.jpg</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
         <is>
           <t>Etta</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>11453005</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr">
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr">
         <is>
           <t>Kasodjdnd</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr">
         <is>
           <t>19.389562,-99.195197</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>Calle: ETTA 6 num int: no tiene Col: Lomas de Becerra S1</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>2026-03-09T17:18:28.181Z</t>
         </is>
@@ -930,53 +966,57 @@
           <t>fotos/maria_de_los_angeles_basurto/device-kv02so/1773076721792-fhb42_2.jpg</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>28</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Eta</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
+          <t>Eta</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>11453001</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Emhg230578mdfrnsoo</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr">
         <is>
           <t>19.389592,-99.195213</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>Calle: calle eta mz 1 num int: lt 2 Col: Lomas de Becerra S1</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>2026-03-09T17:18:41.808Z</t>
         </is>
@@ -1033,49 +1073,53 @@
           <t>fotos/ines_pacheco/device-z9p72n/1773076886443-evkzq_2.jpg</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>31</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Etta</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
+          <t>Etta</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>11453005</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr">
         <is>
           <t>Sosjdidkmflfll</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr">
         <is>
           <t>19.389573,-99.195197</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>Calle: Etta mz. 2 num int: lote 3 Col: Lomas de Becerra S1</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>2026-03-09T17:22:41.521Z</t>
         </is>
@@ -1132,53 +1176,57 @@
           <t>fotos/maria_de_los_angeles_basurto/device-kv02so/1773076963536-avvic_2.jpg</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
         <is>
           <t>Principal</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>10385023</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr">
         <is>
           <t>Int. 1</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Mahtmdf271198hsrn05</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr">
         <is>
           <t>19.389588,-99.195220</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>Calle: principal  8 num int: 1 Col: Lomas de Becerra S1</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2026-03-09T17:22:43.569Z</t>
         </is>
@@ -1235,49 +1283,53 @@
           <t>fotos/ines_pacheco/device-z9p72n/1773077122877-ihvud_2.jpg</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
         <is>
           <t>Andador 2</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>10385023</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr">
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr">
         <is>
           <t>KHDIYDOYFIYZITZIT</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr">
         <is>
           <t>19.389546,-99.195200</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>Calle: andador 2  4 num int:  Col: Lomas de Becerra S1</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>2026-03-09T17:25:22.878Z</t>
         </is>
@@ -1334,53 +1386,57 @@
           <t>fotos/maria_de_los_angeles_basurto/device-kv02so/1773077186211-w4ool_2.jpg</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
         <is>
           <t>Capa</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>11453001</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>Int. 3</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr">
         <is>
           <t>Rila230467mhgsrb07</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr">
         <is>
           <t>19.389594,-99.195209</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>Calle: calle capa 3 num int: 3 Col: Lomas de Becerra S1</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>2026-03-09T17:26:26.223Z</t>
         </is>
@@ -1437,49 +1493,53 @@
           <t>fotos/ines_pacheco/device-z9p72n/1773077281530-13zzd_2.jpg</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
         <is>
           <t>Morelos 6A</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>11453047</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr">
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr">
         <is>
           <t>IGC96G96GUPGUP</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr">
         <is>
           <t>19.389559,-99.195191</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>Calle: calle  morelos  6A num int: 28 Col: Lomas de Becerra S1</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>2026-03-09T17:28:01.530Z</t>
         </is>
@@ -1536,53 +1596,57 @@
           <t>fotos/maria_de_los_angeles_basurto/device-kv02so/1773077369199-irztr_2.jpg</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>53</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>Eta</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
+          <t>Eta</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>11453001</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>Int. 18</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Lehm431020HHGRRR15</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr">
         <is>
           <t>19.389592,-99.195223</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>Calle: calle eta mz 2 num int: lote18 Col: Lomas de Becerra S1</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>2026-03-09T17:29:29.213Z</t>
         </is>
@@ -1639,53 +1703,57 @@
           <t>fotos/maria_de_los_angeles_basurto/device-kv02so/1773077506448-35or9_2.jpg</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>31</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Omicron</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
+          <t>Omicron</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>11453024</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Numl120789mdfgrsn01</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr">
         <is>
           <t>19.389574,-99.195211</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>Calle: OMICRON MZ6 num int: LT10 Col: Lomas de Becerra S1</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>2026-03-09T17:31:46.488Z</t>
         </is>
@@ -1742,49 +1810,53 @@
           <t>fotos/ines_pacheco/device-z9p72n/1773077818445-o9t3x_2.jpg</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
         <is>
           <t>Omicron</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>2 - 2</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>11453024</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr">
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr">
         <is>
           <t>JADIGLGLSMSK</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr">
         <is>
           <t>19.389574,-99.195189</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>Calle: omicron 2 num int: 2 Col: Lomas de Becerra S1</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="Y14" t="inlineStr">
         <is>
           <t>2026-03-09T17:36:58.445Z</t>
         </is>
@@ -1841,49 +1913,53 @@
           <t>fotos/ines_pacheco/device-z9p72n/1773077939013-u8kge_2.jpg</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
         <is>
           <t>Antigua via la venta</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>71</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>11453047</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr">
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr">
         <is>
           <t>JAQKJQIWBSIHI</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr">
         <is>
           <t>19.389554,-99.195185</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>Calle: antigua vía laventa 71 num int: 0 Col: Lomas de Becerra S1</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="Y15" t="inlineStr">
         <is>
           <t>2026-03-09T17:38:59.014Z</t>
         </is>
@@ -1940,45 +2016,49 @@
           <t>fotos/maria_de_los_angeles_basurto/device-kv02so/1773078212848-kpdln_2.jpg</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
         <is>
           <t>Cda. Tehuatepec</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>Maum650918mhgrt00</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr">
         <is>
           <t>19.389574,-99.195209</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr">
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr">
         <is>
           <t>2026-03-09T17:43:32.892Z</t>
         </is>
@@ -2035,53 +2115,57 @@
           <t>fotos/maria_de_los_angeles_basurto/device-kv02so/1773078376023-8v971_2.jpg</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>23</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>Eta</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
+          <t>Eta</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>11453001</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Bogg831203mdfhgrbm07</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr">
         <is>
           <t>19.389585,-99.195207</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>Calle: calle eta me 1 lote 9 num int:  Col: Lomas de Becerra S1</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="Y17" t="inlineStr">
         <is>
           <t>2026-03-09T17:46:16.066Z</t>
         </is>

--- a/salidas/CONSOLIDADO.xlsx
+++ b/salidas/CONSOLIDADO.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y17"/>
+  <dimension ref="A1:Y18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2171,6 +2171,133 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1773085006116-18aeo</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>FREDY FLORES NAHUACATL</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>5567439014</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>3041784</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Cynthya Kraouss Vilchis</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>5566778833</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>ajugdgydte@aisuuew.com</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>fotos/fredy_flores_nahuacatl/device-hks7j6/FEOIBA88723JAIIHDHS_frontal.jpg</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fotos/fredy_flores_nahuacatl/device-hks7j6/FEOIBA88723JAIIHDHS_reverso.jpg</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fotos/fredy_flores_nahuacatl/device-hks7j6/FEOIBA88723JAIIHDHS_comprobante.jpg</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Canario</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>12216012</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>FEOIBA88723JAIIHDHS</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>TOLTECA</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>09812</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>19.389542,-99.195124</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Calle: Savi 4 num int: 145 Col: Pueblo Santa Lucia</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-03-09T19:48:55.124Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/salidas/CONSOLIDADO.xlsx
+++ b/salidas/CONSOLIDADO.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y18"/>
+  <dimension ref="A1:Z18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,15 +529,20 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
+          <t>descripcion_vivienda</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
           <t>coordenadas_gps</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>direccion_base</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>fecha_captura</t>
         </is>
@@ -615,12 +620,13 @@
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr">
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Calle: calle eta mz 2 num int: lote18 Col: Lomas de Becerra S1</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>2026-03-05T20:56:26.658Z</t>
         </is>
@@ -698,12 +704,13 @@
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr">
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Calle: calle eta mz 1 num int: lt 2 Col: Lomas de Becerra S1</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>2026-03-05T20:57:40.937Z</t>
         </is>
@@ -796,17 +803,18 @@
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr">
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
         <is>
           <t>19.389539,-99.195183</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Calle: morelos 12 num int: 9 Col: Lomas de Becerra S1</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>2026-03-09T17:15:55.959Z</t>
         </is>
@@ -899,17 +907,18 @@
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr">
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
         <is>
           <t>19.389562,-99.195197</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Calle: ETTA 6 num int: no tiene Col: Lomas de Becerra S1</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>2026-03-09T17:18:28.181Z</t>
         </is>
@@ -1006,17 +1015,18 @@
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr">
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
         <is>
           <t>19.389592,-99.195213</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Calle: calle eta mz 1 num int: lt 2 Col: Lomas de Becerra S1</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>2026-03-09T17:18:41.808Z</t>
         </is>
@@ -1109,17 +1119,18 @@
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr">
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
         <is>
           <t>19.389573,-99.195197</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Calle: Etta mz. 2 num int: lote 3 Col: Lomas de Becerra S1</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>2026-03-09T17:22:41.521Z</t>
         </is>
@@ -1216,17 +1227,18 @@
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr">
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
         <is>
           <t>19.389588,-99.195220</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Calle: principal  8 num int: 1 Col: Lomas de Becerra S1</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>2026-03-09T17:22:43.569Z</t>
         </is>
@@ -1319,17 +1331,18 @@
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr">
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
         <is>
           <t>19.389546,-99.195200</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Calle: andador 2  4 num int:  Col: Lomas de Becerra S1</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>2026-03-09T17:25:22.878Z</t>
         </is>
@@ -1426,17 +1439,18 @@
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr">
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
         <is>
           <t>19.389594,-99.195209</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Calle: calle capa 3 num int: 3 Col: Lomas de Becerra S1</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Z10" t="inlineStr">
         <is>
           <t>2026-03-09T17:26:26.223Z</t>
         </is>
@@ -1529,17 +1543,18 @@
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr">
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
         <is>
           <t>19.389559,-99.195191</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Calle: calle  morelos  6A num int: 28 Col: Lomas de Becerra S1</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>2026-03-09T17:28:01.530Z</t>
         </is>
@@ -1636,17 +1651,18 @@
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr">
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
         <is>
           <t>19.389592,-99.195223</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Calle: calle eta mz 2 num int: lote18 Col: Lomas de Becerra S1</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>2026-03-09T17:29:29.213Z</t>
         </is>
@@ -1743,17 +1759,18 @@
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr">
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
         <is>
           <t>19.389574,-99.195211</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>Calle: OMICRON MZ6 num int: LT10 Col: Lomas de Becerra S1</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>2026-03-09T17:31:46.488Z</t>
         </is>
@@ -1846,17 +1863,18 @@
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr">
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
         <is>
           <t>19.389574,-99.195189</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
+      <c r="Y14" t="inlineStr">
         <is>
           <t>Calle: omicron 2 num int: 2 Col: Lomas de Becerra S1</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>2026-03-09T17:36:58.445Z</t>
         </is>
@@ -1949,17 +1967,18 @@
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr">
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
         <is>
           <t>19.389554,-99.195185</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
+      <c r="Y15" t="inlineStr">
         <is>
           <t>Calle: antigua vía laventa 71 num int: 0 Col: Lomas de Becerra S1</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>2026-03-09T17:38:59.014Z</t>
         </is>
@@ -2052,13 +2071,14 @@
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr">
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
         <is>
           <t>19.389574,-99.195209</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr">
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr">
         <is>
           <t>2026-03-09T17:43:32.892Z</t>
         </is>
@@ -2155,17 +2175,18 @@
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr">
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
         <is>
           <t>19.389585,-99.195207</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="Y17" t="inlineStr">
         <is>
           <t>Calle: calle eta me 1 lote 9 num int:  Col: Lomas de Becerra S1</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>2026-03-09T17:46:16.066Z</t>
         </is>
@@ -2282,17 +2303,18 @@
           <t>09812</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
         <is>
           <t>19.389542,-99.195124</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
+      <c r="Y18" t="inlineStr">
         <is>
           <t>Calle: Savi 4 num int: 145 Col: Pueblo Santa Lucia</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>2026-03-09T19:48:55.124Z</t>
         </is>

--- a/salidas/CONSOLIDADO.xlsx
+++ b/salidas/CONSOLIDADO.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z18"/>
+  <dimension ref="A1:Z19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2320,6 +2320,138 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1773096533878-s592t</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>FREDY FLORES NAHUACATL</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>5567439014</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>3061133</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>MARIANA CASTILLO</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>55652354212</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>sgdhdtgff@gmail.com</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>fotos/fredy_flores_nahuacatl/device-vyc49c/FHIIDB99888234HJDKKSH_frontal.jpg</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fotos/fredy_flores_nahuacatl/device-vyc49c/FHIIDB99888234HJDKKSH_reverso.jpg</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fotos/fredy_flores_nahuacatl/device-vyc49c/FHIIDB99888234HJDKKSH_comprobante.jpg</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>MORELOS</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>6A_28</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>11453047</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>SN</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>SN</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>FHIIDB99888234HJDKKSH</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>LOMAS DE BECERRA</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>01287</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>CASA CON FACHADA ROJA, FRENTE A TIENDA.</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>19.389476,-99.195108</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Calle: calle  morelos  6A num int: 28 Col: Lomas de Becerra S1</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>2026-03-09T22:48:53.879Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/salidas/CONSOLIDADO.xlsx
+++ b/salidas/CONSOLIDADO.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z19"/>
+  <dimension ref="A1:Z10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -719,12 +719,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1773076555958-28bsx</t>
+          <t>1773076721792-fhb42</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>INES PACHECO</t>
+          <t>MARIA DE LOS ANGELES BASURTO</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -734,43 +734,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2767127</t>
+          <t>2767500</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>consuelo enriques mesa</t>
+          <t>emelia hernandez becerra</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>64</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>5555555555</t>
+          <t>55638526</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>consueloenmes@gmail.com</t>
+          <t>emelia.hernandez@gmail.com</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>fotos/ines_pacheco/device-z9p72n/1773076555958-28bsx_1.jpg</t>
+          <t>fotos/maria_de_los_angeles_basurto/device-kv02so/1773076721792-fhb42_1.jpg</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fotos/ines_pacheco/device-z9p72n/1773076555958-28bsx_2.jpg</t>
+          <t>fotos/maria_de_los_angeles_basurto/device-kv02so/1773076721792-fhb42_2.jpg</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>28</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -781,24 +781,28 @@
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Morelos</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>12 - 9</t>
-        </is>
-      </c>
+          <t>Eta</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>11453047</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
+          <t>11453001</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>Lhdi6doyf7</t>
+          <t>Emhg230578mdfrnsoo</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -806,29 +810,29 @@
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
-          <t>19.389539,-99.195183</t>
+          <t>19.389592,-99.195213</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Calle: morelos 12 num int: 9 Col: Lomas de Becerra S1</t>
+          <t>Calle: calle eta mz 1 num int: lt 2 Col: Lomas de Becerra S1</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-03-09T17:15:55.959Z</t>
+          <t>2026-03-09T17:18:41.808Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1773076708181-luodg</t>
+          <t>1773076963536-avvic</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>INES PACHECO</t>
+          <t>MARIA DE LOS ANGELES BASURTO</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -838,71 +842,75 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2767248</t>
+          <t>2768296</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>PAULA DEL VALLE SANDOVAL</t>
+          <t>maría  blas  silverio</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>45</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>5555555551</t>
+          <t>5511788745</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>delvallepau@hotmail.com</t>
+          <t>mariablassil@gmail.com</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>fotos/ines_pacheco/device-z9p72n/1773076708181-luodg_1.jpg</t>
+          <t>fotos/maria_de_los_angeles_basurto/device-kv02so/1773076963536-avvic_1.jpg</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fotos/ines_pacheco/device-z9p72n/1773076708181-luodg_2.jpg</t>
+          <t>fotos/maria_de_los_angeles_basurto/device-kv02so/1773076963536-avvic_2.jpg</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>25</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>28</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Etta</t>
+          <t>Principal</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>11453005</t>
+          <t>10385023</t>
         </is>
       </c>
       <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Int. 1</t>
+        </is>
+      </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>Kasodjdnd</t>
+          <t>Mahtmdf271198hsrn05</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -910,24 +918,24 @@
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
-          <t>19.389562,-99.195197</t>
+          <t>19.389588,-99.195220</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Calle: ETTA 6 num int: no tiene Col: Lomas de Becerra S1</t>
+          <t>Calle: principal  8 num int: 1 Col: Lomas de Becerra S1</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2026-03-09T17:18:28.181Z</t>
+          <t>2026-03-09T17:22:43.569Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1773076721792-fhb42</t>
+          <t>1773077186211-w4ool</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -942,57 +950,61 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2767500</t>
+          <t>2767254</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>emelia hernandez becerra</t>
+          <t>Alicia rico leon</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>60</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>55638526</t>
+          <t>5521689065</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>emelia.hernandez@gmail.com</t>
+          <t>alirile@gmail.com</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>fotos/maria_de_los_angeles_basurto/device-kv02so/1773076721792-fhb42_1.jpg</t>
+          <t>fotos/maria_de_los_angeles_basurto/device-kv02so/1773077186211-w4ool_1.jpg</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fotos/maria_de_los_angeles_basurto/device-kv02so/1773076721792-fhb42_2.jpg</t>
+          <t>fotos/maria_de_los_angeles_basurto/device-kv02so/1773077186211-w4ool_2.jpg</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>24</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>34</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Eta</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr"/>
+          <t>Capa</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="Q6" t="inlineStr">
         <is>
           <t>11453001</t>
@@ -1000,17 +1012,13 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Int. 3</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr">
         <is>
-          <t>Emhg230578mdfrnsoo</t>
+          <t>Rila230467mhgsrb07</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1018,29 +1026,29 @@
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
-          <t>19.389592,-99.195213</t>
+          <t>19.389594,-99.195209</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Calle: calle eta mz 1 num int: lt 2 Col: Lomas de Becerra S1</t>
+          <t>Calle: calle capa 3 num int: 3 Col: Lomas de Becerra S1</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2026-03-09T17:18:41.808Z</t>
+          <t>2026-03-09T17:26:26.223Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1773076886443-evkzq</t>
+          <t>1773077369199-irztr</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>INES PACHECO</t>
+          <t>MARIA DE LOS ANGELES BASURTO</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1050,60 +1058,60 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3060955</t>
+          <t>3061071</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>lourdes</t>
+          <t>Maria isabel ledezma salas</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>92</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>5555555552</t>
+          <t>5523256789</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>lulu50@gmail.com</t>
+          <t>mari.lema@gmail.com</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>fotos/ines_pacheco/device-z9p72n/1773076886443-evkzq_1.jpg</t>
+          <t>fotos/maria_de_los_angeles_basurto/device-kv02so/1773077369199-irztr_1.jpg</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fotos/ines_pacheco/device-z9p72n/1773076886443-evkzq_2.jpg</t>
+          <t>fotos/maria_de_los_angeles_basurto/device-kv02so/1773077369199-irztr_2.jpg</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>53</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Etta</t>
+          <t>Eta</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>11453005</t>
+          <t>11453001</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1111,10 +1119,14 @@
           <t>2</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr"/>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>Int. 18</t>
+        </is>
+      </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>Sosjdidkmflfll</t>
+          <t>Lehm431020HHGRRR15</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1122,24 +1134,24 @@
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
-          <t>19.389573,-99.195197</t>
+          <t>19.389592,-99.195223</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Calle: Etta mz. 2 num int: lote 3 Col: Lomas de Becerra S1</t>
+          <t>Calle: calle eta mz 2 num int: lote18 Col: Lomas de Becerra S1</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2026-03-09T17:22:41.521Z</t>
+          <t>2026-03-09T17:29:29.213Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1773076963536-avvic</t>
+          <t>1773077506448-35or9</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1154,75 +1166,75 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2768296</t>
+          <t>2767282</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>maría  blas  silverio</t>
+          <t>MARÍA  LETICIA  NUÑEZ AGUILAR</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>62</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>5511788745</t>
+          <t>5534678954</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>mariablassil@gmail.com</t>
+          <t>malenu@gmail.com</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>fotos/maria_de_los_angeles_basurto/device-kv02so/1773076963536-avvic_1.jpg</t>
+          <t>fotos/maria_de_los_angeles_basurto/device-kv02so/1773077506448-35or9_1.jpg</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fotos/maria_de_los_angeles_basurto/device-kv02so/1773076963536-avvic_2.jpg</t>
+          <t>fotos/maria_de_los_angeles_basurto/device-kv02so/1773077506448-35or9_2.jpg</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>31</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Principal</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>Omicron</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>10385023</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr"/>
+          <t>11453024</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>Int. 1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>Mahtmdf271198hsrn05</t>
+          <t>Numl120789mdfgrsn01</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1230,29 +1242,29 @@
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
-          <t>19.389588,-99.195220</t>
+          <t>19.389574,-99.195211</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Calle: principal  8 num int: 1 Col: Lomas de Becerra S1</t>
+          <t>Calle: OMICRON MZ6 num int: LT10 Col: Lomas de Becerra S1</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2026-03-09T17:22:43.569Z</t>
+          <t>2026-03-09T17:31:46.488Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1773077122877-ihvud</t>
+          <t>1773078212848-kpdln</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>INES PACHECO</t>
+          <t>MARIA DE LOS ANGELES BASURTO</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1262,71 +1274,71 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2768120</t>
+          <t>2767132</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Maria de lourdes gonzales salazar</t>
+          <t>DEMETRIA MINERVA BECERRA DIAZ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>58</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>555555553</t>
+          <t>5527315689</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>malugo@aol.com</t>
+          <t>demmihy@gmail.com</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>fotos/ines_pacheco/device-z9p72n/1773077122877-ihvud_1.jpg</t>
+          <t>fotos/maria_de_los_angeles_basurto/device-kv02so/1773078212848-kpdln_1.jpg</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fotos/ines_pacheco/device-z9p72n/1773077122877-ihvud_2.jpg</t>
+          <t>fotos/maria_de_los_angeles_basurto/device-kv02so/1773078212848-kpdln_2.jpg</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>34</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>19</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Andador 2</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>10385023</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
+          <t>Cda. Tehuatepec</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>KHDIYDOYFIYZITZIT</t>
+          <t>Maum650918mhgrt00</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1334,24 +1346,20 @@
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr">
         <is>
-          <t>19.389546,-99.195200</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Calle: andador 2  4 num int:  Col: Lomas de Becerra S1</t>
-        </is>
-      </c>
+          <t>19.389574,-99.195209</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2026-03-09T17:25:22.878Z</t>
+          <t>2026-03-09T17:43:32.892Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1773077186211-w4ool</t>
+          <t>1773078376023-8v971</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1366,61 +1374,57 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2767254</t>
+          <t>2767499</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Alicia rico leon</t>
+          <t>gabriela borja garduño</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>5521689065</t>
+          <t>5567890345</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>alirile@gmail.com</t>
+          <t>gaboga45@gmail.com</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>fotos/maria_de_los_angeles_basurto/device-kv02so/1773077186211-w4ool_1.jpg</t>
+          <t>fotos/maria_de_los_angeles_basurto/device-kv02so/1773078376023-8v971_1.jpg</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fotos/maria_de_los_angeles_basurto/device-kv02so/1773077186211-w4ool_2.jpg</t>
+          <t>fotos/maria_de_los_angeles_basurto/device-kv02so/1773078376023-8v971_2.jpg</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>23</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Capa</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Eta</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr">
         <is>
           <t>11453001</t>
@@ -1428,13 +1432,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Int. 3</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>Rila230467mhgsrb07</t>
+          <t>Bogg831203mdfhgrbm07</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1442,1013 +1450,17 @@
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
-          <t>19.389594,-99.195209</t>
+          <t>19.389585,-99.195207</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Calle: calle capa 3 num int: 3 Col: Lomas de Becerra S1</t>
+          <t>Calle: calle eta me 1 lote 9 num int:  Col: Lomas de Becerra S1</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2026-03-09T17:26:26.223Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>1773077281530-13zzd</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>INES PACHECO</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>5555555555</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>3061133</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>mariana castillo</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>555555556</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>marcast@outlook.com</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>fotos/ines_pacheco/device-z9p72n/1773077281530-13zzd_1.jpg</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fotos/ines_pacheco/device-z9p72n/1773077281530-13zzd_2.jpg</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>Morelos 6A</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>11453047</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>IGC96G96GUPGUP</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>19.389559,-99.195191</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Calle: calle  morelos  6A num int: 28 Col: Lomas de Becerra S1</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>2026-03-09T17:28:01.530Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>1773077369199-irztr</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>MARIA DE LOS ANGELES BASURTO</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>5555555555</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>3061071</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Maria isabel ledezma salas</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>5523256789</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>mari.lema@gmail.com</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>fotos/maria_de_los_angeles_basurto/device-kv02so/1773077369199-irztr_1.jpg</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fotos/maria_de_los_angeles_basurto/device-kv02so/1773077369199-irztr_2.jpg</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>Eta</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>11453001</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>Int. 18</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Lehm431020HHGRRR15</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>19.389592,-99.195223</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Calle: calle eta mz 2 num int: lote18 Col: Lomas de Becerra S1</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>2026-03-09T17:29:29.213Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>1773077506448-35or9</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>MARIA DE LOS ANGELES BASURTO</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>5555555555</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2767282</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>MARÍA  LETICIA  NUÑEZ AGUILAR</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>5534678954</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>malenu@gmail.com</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>fotos/maria_de_los_angeles_basurto/device-kv02so/1773077506448-35or9_1.jpg</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fotos/maria_de_los_angeles_basurto/device-kv02so/1773077506448-35or9_2.jpg</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>Omicron</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>11453024</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Numl120789mdfgrsn01</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>19.389574,-99.195211</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Calle: OMICRON MZ6 num int: LT10 Col: Lomas de Becerra S1</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>2026-03-09T17:31:46.488Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>1773077818445-o9t3x</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>INES PACHECO</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>5555555555</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>3061089</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>cristina sanchez</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>5555555557</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>sanchezcris@gmail.com</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>fotos/ines_pacheco/device-z9p72n/1773077818445-o9t3x_1.jpg</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fotos/ines_pacheco/device-z9p72n/1773077818445-o9t3x_2.jpg</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>Omicron</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>2 - 2</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>11453024</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>JADIGLGLSMSK</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>19.389574,-99.195189</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Calle: omicron 2 num int: 2 Col: Lomas de Becerra S1</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>2026-03-09T17:36:58.445Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>1773077939013-u8kge</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>INES PACHECO</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>5555555555</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2767187</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>lucinaco,estoy martinez</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>5555555558</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>luciestmart@hotmail.com</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>fotos/ines_pacheco/device-z9p72n/1773077939013-u8kge_1.jpg</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fotos/ines_pacheco/device-z9p72n/1773077939013-u8kge_2.jpg</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>Antigua via la venta</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>11453047</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>JAQKJQIWBSIHI</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>19.389554,-99.195185</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Calle: antigua vía laventa 71 num int: 0 Col: Lomas de Becerra S1</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>2026-03-09T17:38:59.014Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>1773078212848-kpdln</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>MARIA DE LOS ANGELES BASURTO</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>5555555555</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2767132</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>DEMETRIA MINERVA BECERRA DIAZ</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>5527315689</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>demmihy@gmail.com</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>fotos/maria_de_los_angeles_basurto/device-kv02so/1773078212848-kpdln_1.jpg</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fotos/maria_de_los_angeles_basurto/device-kv02so/1773078212848-kpdln_2.jpg</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>Cda. Tehuatepec</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Maum650918mhgrt00</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>19.389574,-99.195209</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>2026-03-09T17:43:32.892Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>1773078376023-8v971</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>MARIA DE LOS ANGELES BASURTO</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>5555555555</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2767499</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>gabriela borja garduño</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>5567890345</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>gaboga45@gmail.com</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>fotos/maria_de_los_angeles_basurto/device-kv02so/1773078376023-8v971_1.jpg</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fotos/maria_de_los_angeles_basurto/device-kv02so/1773078376023-8v971_2.jpg</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>Eta</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>11453001</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Bogg831203mdfhgrbm07</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>19.389585,-99.195207</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Calle: calle eta me 1 lote 9 num int:  Col: Lomas de Becerra S1</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
           <t>2026-03-09T17:46:16.066Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>1773085006116-18aeo</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>FREDY FLORES NAHUACATL</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>5567439014</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>3041784</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Cynthya Kraouss Vilchis</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>5566778833</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>ajugdgydte@aisuuew.com</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>fotos/fredy_flores_nahuacatl/device-hks7j6/FEOIBA88723JAIIHDHS_frontal.jpg</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fotos/fredy_flores_nahuacatl/device-hks7j6/FEOIBA88723JAIIHDHS_reverso.jpg</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>fotos/fredy_flores_nahuacatl/device-hks7j6/FEOIBA88723JAIIHDHS_comprobante.jpg</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>Canario</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>12216012</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>FEOIBA88723JAIIHDHS</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>TOLTECA</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>09812</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>19.389542,-99.195124</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Calle: Savi 4 num int: 145 Col: Pueblo Santa Lucia</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>2026-03-09T19:48:55.124Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>1773096533878-s592t</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>FREDY FLORES NAHUACATL</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>5567439014</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>3061133</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>MARIANA CASTILLO</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>55652354212</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>sgdhdtgff@gmail.com</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>fotos/fredy_flores_nahuacatl/device-vyc49c/FHIIDB99888234HJDKKSH_frontal.jpg</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fotos/fredy_flores_nahuacatl/device-vyc49c/FHIIDB99888234HJDKKSH_reverso.jpg</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>fotos/fredy_flores_nahuacatl/device-vyc49c/FHIIDB99888234HJDKKSH_comprobante.jpg</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>MORELOS</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>6A_28</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>11453047</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>SN</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>SN</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>FHIIDB99888234HJDKKSH</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>LOMAS DE BECERRA</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>01287</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>CASA CON FACHADA ROJA, FRENTE A TIENDA.</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>19.389476,-99.195108</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Calle: calle  morelos  6A num int: 28 Col: Lomas de Becerra S1</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>2026-03-09T22:48:53.879Z</t>
         </is>
       </c>
     </row>

--- a/salidas/CONSOLIDADO.xlsx
+++ b/salidas/CONSOLIDADO.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z1"/>
+  <dimension ref="A1:Z10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -545,6 +545,1126 @@
       <c r="Z1" t="inlineStr">
         <is>
           <t>fecha_captura</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1773162712096-y5qa4</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ISIDRO DIAZ CRUZ</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>5646653398</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>3041695</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Maria Nicolasa Carmona Segundo</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5635357162</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>carmonanico912@gmail.com</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>fotos/isidro_diaz_cruz/device-1mw0yj/CASN720910MMCRGC00_frontal.jpg</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fotos/isidro_diaz_cruz/device-1mw0yj/CASN720910MMCRGC00_reverso.jpg</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>fotos/isidro_diaz_cruz/device-1mw0yj/CASN720910MMCRGC00_comprobante.jpg</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Saabi</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>12216002</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>CASN720910MMCRGC00</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Miguel Gaona Armenta</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>01500</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Casa amarilla frente a los juegos</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>19.355716,-99.250698</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Calle: Saabi mz. 4 num int: lt. 147 Col: Pueblo Santa Lucia</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>2026-03-10T17:11:52.101Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1773163050773-irmr9</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ALISON YARET MORALES VALENCIA</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>5576032821</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>3041681</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ana maría maximino de jesus</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>5566340146</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>anamariamaximinodejesus@gmail.com</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>fotos/alison_yaret_morales_valencia/device-9kcl7j/MAJA661029MDFXSN03_frontal.jpg</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fotos/alison_yaret_morales_valencia/device-9kcl7j/MAJA661029MDFXSN03_reverso.jpg</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fotos/alison_yaret_morales_valencia/device-9kcl7j/MAJA661029MDFXSN03_comprobante.jpg</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Saabi</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>12216002</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>MAJA661029MDFXSN03</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Miguel Gaona Armenta</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>01500</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Fachada de ladrillo,puerta de madera con lona blanca</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>19.355592,-99.250544</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Calle: saavi  mz3 num int: lt166 Col: Pueblo Santa Lucia</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>2026-03-10T17:17:30.781Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1773166573056-ppej3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ALISON YARET MORALES VALENCIA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>5576032821</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>3041616</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>francisca pedro blas</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>5584240053</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>pedrofrancisca651@gmail.com</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>fotos/alison_yaret_morales_valencia/device-9kcl7j/PEBF690303MQTDLR04_frontal.jpg</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fotos/alison_yaret_morales_valencia/device-9kcl7j/PEBF690303MQTDLR04_reverso.jpg</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fotos/alison_yaret_morales_valencia/device-9kcl7j/PEBF690303MQTDLR04_comprobante.jpg</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>12216045</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>PEBF690303MQTDLR04</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Tierra nueva claxomulco</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>01500</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>19.355449,-99.248343</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Calle: bellana 66 num int: lote 15 Col: Pueblo Santa Lucia</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>2026-03-10T18:16:13.069Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1773166594639-dx8cz</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ISIDRO DIAZ CRUZ</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>5646653398</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>3041617</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sara Quirino Pedro</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>5528387002</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>quirinosara15@gmail.com</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>fotos/isidro_diaz_cruz/device-1mw0yj/QUPS860407MQTRDR08_frontal.jpg</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fotos/isidro_diaz_cruz/device-1mw0yj/QUPS860407MQTRDR08_reverso.jpg</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fotos/isidro_diaz_cruz/device-1mw0yj/QUPS860407MQTRDR08_comprobante.jpg</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Prol Arrabales</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>12216045</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>QUPS860407MQTRDR08</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Tierra Nueva Tlaxomulco</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>01500</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Casa de madera en andador de tierra.</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>19.355450,-99.248391</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Calle: beĺlana 66 num int: mz 15 Col: Pueblo Santa Lucia</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>2026-03-10T18:16:34.641Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1773167120609-in3qd</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ALISON YARET MORALES VALENCIA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>5576032821</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>3041606</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Julia Maria Gonzalez Valdez</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>5536788871</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Juliagova20@gmail.com</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>fotos/alison_yaret_morales_valencia/device-9kcl7j/JOVJ750220MDFNLL06_frontal.jpg</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fotos/alison_yaret_morales_valencia/device-9kcl7j/JOVJ750220MDFNLL06_reverso.jpg</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fotos/alison_yaret_morales_valencia/device-9kcl7j/JOVJ750220MDFNLL06_comprobante.jpg</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Prolongación arrabales</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>12216045</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>JOVJ750220MDFNLL06</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>01500</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>19.355590,-99.248271</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Calle: Prolongación  Arrabales  64 num int: no Col: Pueblo Santa Lucia</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>2026-03-10T18:25:20.624Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1773168216149-fx1b8</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ISIDRO DIAZ CRUZ</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>5646653398</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>3070761</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Reyna García González</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>5560899508</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>tecanalondra718@gmial.com</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>fotos/isidro_diaz_cruz/device-1mw0yj/GAGR730405MHGRNY02_frontal.jpg</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fotos/isidro_diaz_cruz/device-1mw0yj/GAGR730405MHGRNY02_reverso.jpg</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fotos/isidro_diaz_cruz/device-1mw0yj/GAGR730405MHGRNY02_comprobante.jpg</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Continuación Arrabales</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>12216038</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>GAGR730405MHGRNY02</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Tierra Nueva Tlaxomulco</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>01500</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Casa en andador de tierra con una tienda puerta de metal gris</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>19.354633,-99.249421</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Calle: CONTINUACION A ARRABALES 9 num int:  Col: Pueblo Santa Lucia</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>2026-03-10T18:43:36.151Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1773170561338-ocrit</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ALISON YARET MORALES VALENCIA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>5576032821</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>3041780</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Yolanda ramos delgado</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>5526781260</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>yolaramosd41@gmail</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>fotos/alison_yaret_morales_valencia/device-9kcl7j/RADY800603MDFMLL04_frontal.jpg</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fotos/alison_yaret_morales_valencia/device-9kcl7j/RADY800603MDFMLL04_reverso.jpg</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fotos/alison_yaret_morales_valencia/device-9kcl7j/RADY800603MDFMLL04_comprobante.jpg</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Chabacano</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>12216014</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>RADY800603MDFMLL04</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Pueblo santa Lucia</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>01500</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>19.356110,-99.249671</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Calle: Calle chabacano  5 num int: 5 Col: Pueblo Santa Lucia</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>2026-03-10T19:22:41.346Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1773171795463-m62sg</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ALISON YARET MORALES VALENCIA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>5576032821</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>3041836</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Maria del Carmen ALEJANDRA GOMEZ MACIAS</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>54234345</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>fotos/alison_yaret_morales_valencia/device-9kcl7j/GOMC590717MDFMCR09_frontal.jpg</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fotos/alison_yaret_morales_valencia/device-9kcl7j/GOMC590717MDFMCR09_reverso.jpg</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fotos/alison_yaret_morales_valencia/device-9kcl7j/GOMC590717MDFMCR09_comprobante.jpg</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Callejón Allende</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>12216013</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>GOMC590717MDFMCR09</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Santa Lucia</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>01500</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Esquina ,tiene puesto de artesanías</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>19.356837,-99.250615</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Calle: CALLEJON ALLENDE  3 num int: S/N Col: Pueblo Santa Lucia</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>2026-03-10T19:43:15.468Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1773171913685-7x9bs</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ISIDRO DIAZ CRUZ</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>5646653398</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>3041845</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Guadalupe Baeza Guerrero</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>5549241783</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>fotos/isidro_diaz_cruz/device-1mw0yj/BAGG491223MDFZRD04_frontal.jpg</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fotos/isidro_diaz_cruz/device-1mw0yj/BAGG491223MDFZRD04_reverso.jpg</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fotos/isidro_diaz_cruz/device-1mw0yj/BAGG491223MDFZRD04_comprobante.jpg</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Callejón Allende</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>12216013</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>BAGG491223MDFZRD04</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>La Mora Santa Lucía</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>01500</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Casa amarilla puerta roja justo en la esquina que entre Allende y Av San Isidro</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>19.357095,-99.249925</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Calle: callejon allende  a num int: 1 Col: Pueblo Santa Lucia</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>2026-03-10T19:45:13.689Z</t>
         </is>
       </c>
     </row>

--- a/salidas/CONSOLIDADO.xlsx
+++ b/salidas/CONSOLIDADO.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z10"/>
+  <dimension ref="A1:AE10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,105 +444,130 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>nombre_base</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>apellido_paterno</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>apellido_materno</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>edad</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>telefono</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>correo_electronico</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>foto_1_path</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>foto_1_url</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
         <is>
           <t>foto_2_path</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>foto_2_url</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
         <is>
           <t>foto_3_path</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>foto_1_kb</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>foto_2_kb</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>foto_3_kb</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>foto_3_url</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
         <is>
           <t>calle</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>numero</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>manzana_inegi</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>manzana</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>lote</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>curp</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>colonia</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>codigo_postal</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>descripcion_vivienda</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>coordenadas_gps</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>latitud</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>longitud</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
         <is>
           <t>direccion_base</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>fecha_captura</t>
         </is>
@@ -574,103 +599,116 @@
           <t>Maria Nicolasa Carmona Segundo</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>5635357162</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>carmonanico912@gmail.com</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>fotos/isidro_diaz_cruz/device-1mw0yj/CASN720910MMCRGC00_frontal.jpg</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/GeomaticaAO/APP_PAPEAO_MGE/main/fotos/isidro_diaz_cruz/device-1mw0yj/CASN720910MMCRGC00_frontal.jpg</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
         <is>
           <t>fotos/isidro_diaz_cruz/device-1mw0yj/CASN720910MMCRGC00_reverso.jpg</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/GeomaticaAO/APP_PAPEAO_MGE/main/fotos/isidro_diaz_cruz/device-1mw0yj/CASN720910MMCRGC00_reverso.jpg</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>fotos/isidro_diaz_cruz/device-1mw0yj/CASN720910MMCRGC00_comprobante.jpg</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/GeomaticaAO/APP_PAPEAO_MGE/main/fotos/isidro_diaz_cruz/device-1mw0yj/CASN720910MMCRGC00_comprobante.jpg</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
         <is>
           <t>Saabi</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr">
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr">
         <is>
           <t>12216002</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>147</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>CASN720910MMCRGC00</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>Miguel Gaona Armenta</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>01500</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>Casa amarilla frente a los juegos</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>19.355716,-99.250698</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>19.355716</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>-99.250698</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
         <is>
           <t>Calle: Saabi mz. 4 num int: lt. 147 Col: Pueblo Santa Lucia</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>2026-03-10T17:11:52.101Z</t>
         </is>
@@ -702,103 +740,116 @@
           <t>ana maría maximino de jesus</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>5566340146</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>anamariamaximinodejesus@gmail.com</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>fotos/alison_yaret_morales_valencia/device-9kcl7j/MAJA661029MDFXSN03_frontal.jpg</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/GeomaticaAO/APP_PAPEAO_MGE/main/fotos/alison_yaret_morales_valencia/device-9kcl7j/MAJA661029MDFXSN03_frontal.jpg</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
         <is>
           <t>fotos/alison_yaret_morales_valencia/device-9kcl7j/MAJA661029MDFXSN03_reverso.jpg</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/GeomaticaAO/APP_PAPEAO_MGE/main/fotos/alison_yaret_morales_valencia/device-9kcl7j/MAJA661029MDFXSN03_reverso.jpg</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>fotos/alison_yaret_morales_valencia/device-9kcl7j/MAJA661029MDFXSN03_comprobante.jpg</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/GeomaticaAO/APP_PAPEAO_MGE/main/fotos/alison_yaret_morales_valencia/device-9kcl7j/MAJA661029MDFXSN03_comprobante.jpg</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
         <is>
           <t>Saabi</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr">
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr">
         <is>
           <t>12216002</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>166</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>MAJA661029MDFXSN03</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>Miguel Gaona Armenta</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>01500</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>Fachada de ladrillo,puerta de madera con lona blanca</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>19.355592,-99.250544</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>19.355592</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>-99.250544</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
         <is>
           <t>Calle: saavi  mz3 num int: lt166 Col: Pueblo Santa Lucia</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>2026-03-10T17:17:30.781Z</t>
         </is>
@@ -830,95 +881,108 @@
           <t>francisca pedro blas</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>5584240053</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>pedrofrancisca651@gmail.com</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>fotos/alison_yaret_morales_valencia/device-9kcl7j/PEBF690303MQTDLR04_frontal.jpg</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/GeomaticaAO/APP_PAPEAO_MGE/main/fotos/alison_yaret_morales_valencia/device-9kcl7j/PEBF690303MQTDLR04_frontal.jpg</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>fotos/alison_yaret_morales_valencia/device-9kcl7j/PEBF690303MQTDLR04_reverso.jpg</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/GeomaticaAO/APP_PAPEAO_MGE/main/fotos/alison_yaret_morales_valencia/device-9kcl7j/PEBF690303MQTDLR04_reverso.jpg</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>fotos/alison_yaret_morales_valencia/device-9kcl7j/PEBF690303MQTDLR04_comprobante.jpg</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr">
         <is>
+          <t>https://raw.githubusercontent.com/GeomaticaAO/APP_PAPEAO_MGE/main/fotos/alison_yaret_morales_valencia/device-9kcl7j/PEBF690303MQTDLR04_comprobante.jpg</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr">
+        <is>
           <t>12216045</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>PEBF690303MQTDLR04</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>Tierra nueva claxomulco</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>01500</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr">
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr">
         <is>
           <t>19.355449,-99.248343</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>19.355449</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>-99.248343</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
         <is>
           <t>Calle: bellana 66 num int: lote 15 Col: Pueblo Santa Lucia</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>2026-03-10T18:16:13.069Z</t>
         </is>
@@ -950,103 +1014,116 @@
           <t>Sara Quirino Pedro</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>5528387002</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>quirinosara15@gmail.com</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>fotos/isidro_diaz_cruz/device-1mw0yj/QUPS860407MQTRDR08_frontal.jpg</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/GeomaticaAO/APP_PAPEAO_MGE/main/fotos/isidro_diaz_cruz/device-1mw0yj/QUPS860407MQTRDR08_frontal.jpg</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>fotos/isidro_diaz_cruz/device-1mw0yj/QUPS860407MQTRDR08_reverso.jpg</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/GeomaticaAO/APP_PAPEAO_MGE/main/fotos/isidro_diaz_cruz/device-1mw0yj/QUPS860407MQTRDR08_reverso.jpg</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
         <is>
           <t>fotos/isidro_diaz_cruz/device-1mw0yj/QUPS860407MQTRDR08_comprobante.jpg</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/GeomaticaAO/APP_PAPEAO_MGE/main/fotos/isidro_diaz_cruz/device-1mw0yj/QUPS860407MQTRDR08_comprobante.jpg</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
         <is>
           <t>Prol Arrabales</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr">
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr">
         <is>
           <t>12216045</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>QUPS860407MQTRDR08</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>Tierra Nueva Tlaxomulco</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>01500</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>Casa de madera en andador de tierra.</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>19.355450,-99.248391</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>19.355450</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>-99.248391</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
         <is>
           <t>Calle: beĺlana 66 num int: mz 15 Col: Pueblo Santa Lucia</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>2026-03-10T18:16:34.641Z</t>
         </is>
@@ -1078,91 +1155,104 @@
           <t>Julia Maria Gonzalez Valdez</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>5536788871</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>Juliagova20@gmail.com</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>fotos/alison_yaret_morales_valencia/device-9kcl7j/JOVJ750220MDFNLL06_frontal.jpg</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/GeomaticaAO/APP_PAPEAO_MGE/main/fotos/alison_yaret_morales_valencia/device-9kcl7j/JOVJ750220MDFNLL06_frontal.jpg</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t>fotos/alison_yaret_morales_valencia/device-9kcl7j/JOVJ750220MDFNLL06_reverso.jpg</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/GeomaticaAO/APP_PAPEAO_MGE/main/fotos/alison_yaret_morales_valencia/device-9kcl7j/JOVJ750220MDFNLL06_reverso.jpg</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>fotos/alison_yaret_morales_valencia/device-9kcl7j/JOVJ750220MDFNLL06_comprobante.jpg</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/GeomaticaAO/APP_PAPEAO_MGE/main/fotos/alison_yaret_morales_valencia/device-9kcl7j/JOVJ750220MDFNLL06_comprobante.jpg</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Prolongación arrabales</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>64</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Prolongación arrabales</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>12216045</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr">
         <is>
           <t>JOVJ750220MDFNLL06</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr">
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr">
         <is>
           <t>01500</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr">
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr">
         <is>
           <t>19.355590,-99.248271</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>19.355590</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>-99.248271</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
         <is>
           <t>Calle: Prolongación  Arrabales  64 num int: no Col: Pueblo Santa Lucia</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>2026-03-10T18:25:20.624Z</t>
         </is>
@@ -1194,99 +1284,112 @@
           <t>Reyna García González</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>5560899508</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>tecanalondra718@gmial.com</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>fotos/isidro_diaz_cruz/device-1mw0yj/GAGR730405MHGRNY02_frontal.jpg</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/GeomaticaAO/APP_PAPEAO_MGE/main/fotos/isidro_diaz_cruz/device-1mw0yj/GAGR730405MHGRNY02_frontal.jpg</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
         <is>
           <t>fotos/isidro_diaz_cruz/device-1mw0yj/GAGR730405MHGRNY02_reverso.jpg</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/GeomaticaAO/APP_PAPEAO_MGE/main/fotos/isidro_diaz_cruz/device-1mw0yj/GAGR730405MHGRNY02_reverso.jpg</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
         <is>
           <t>fotos/isidro_diaz_cruz/device-1mw0yj/GAGR730405MHGRNY02_comprobante.jpg</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/GeomaticaAO/APP_PAPEAO_MGE/main/fotos/isidro_diaz_cruz/device-1mw0yj/GAGR730405MHGRNY02_comprobante.jpg</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
         <is>
           <t>Continuación Arrabales</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>12216038</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr">
         <is>
           <t>GAGR730405MHGRNY02</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>Tierra Nueva Tlaxomulco</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>01500</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>Casa en andador de tierra con una tienda puerta de metal gris</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>19.354633,-99.249421</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>19.354633</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>-99.249421</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
         <is>
           <t>Calle: CONTINUACION A ARRABALES 9 num int:  Col: Pueblo Santa Lucia</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>2026-03-10T18:43:36.151Z</t>
         </is>
@@ -1318,99 +1421,112 @@
           <t>Yolanda ramos delgado</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>5526781260</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>yolaramosd41@gmail</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>fotos/alison_yaret_morales_valencia/device-9kcl7j/RADY800603MDFMLL04_frontal.jpg</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/GeomaticaAO/APP_PAPEAO_MGE/main/fotos/alison_yaret_morales_valencia/device-9kcl7j/RADY800603MDFMLL04_frontal.jpg</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
         <is>
           <t>fotos/alison_yaret_morales_valencia/device-9kcl7j/RADY800603MDFMLL04_reverso.jpg</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/GeomaticaAO/APP_PAPEAO_MGE/main/fotos/alison_yaret_morales_valencia/device-9kcl7j/RADY800603MDFMLL04_reverso.jpg</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>fotos/alison_yaret_morales_valencia/device-9kcl7j/RADY800603MDFMLL04_comprobante.jpg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/GeomaticaAO/APP_PAPEAO_MGE/main/fotos/alison_yaret_morales_valencia/device-9kcl7j/RADY800603MDFMLL04_comprobante.jpg</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
         <is>
           <t>Chabacano</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr">
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr">
         <is>
           <t>12216014</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>RADY800603MDFMLL04</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>Pueblo santa Lucia</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>01500</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr">
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr">
         <is>
           <t>19.356110,-99.249671</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>19.356110</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>-99.249671</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
         <is>
           <t>Calle: Calle chabacano  5 num int: 5 Col: Pueblo Santa Lucia</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>2026-03-10T19:22:41.346Z</t>
         </is>
@@ -1442,103 +1558,116 @@
           <t>Maria del Carmen ALEJANDRA GOMEZ MACIAS</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>54234345</t>
-        </is>
-      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>54234345</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
           <t>fotos/alison_yaret_morales_valencia/device-9kcl7j/GOMC590717MDFMCR09_frontal.jpg</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/GeomaticaAO/APP_PAPEAO_MGE/main/fotos/alison_yaret_morales_valencia/device-9kcl7j/GOMC590717MDFMCR09_frontal.jpg</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
         <is>
           <t>fotos/alison_yaret_morales_valencia/device-9kcl7j/GOMC590717MDFMCR09_reverso.jpg</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/GeomaticaAO/APP_PAPEAO_MGE/main/fotos/alison_yaret_morales_valencia/device-9kcl7j/GOMC590717MDFMCR09_reverso.jpg</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
         <is>
           <t>fotos/alison_yaret_morales_valencia/device-9kcl7j/GOMC590717MDFMCR09_comprobante.jpg</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/GeomaticaAO/APP_PAPEAO_MGE/main/fotos/alison_yaret_morales_valencia/device-9kcl7j/GOMC590717MDFMCR09_comprobante.jpg</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
         <is>
           <t>Callejón Allende</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>12216013</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>GOMC590717MDFMCR09</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>Santa Lucia</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>01500</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>Esquina ,tiene puesto de artesanías</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>19.356837,-99.250615</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>19.356837</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>-99.250615</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
         <is>
           <t>Calle: CALLEJON ALLENDE  3 num int: S/N Col: Pueblo Santa Lucia</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>2026-03-10T19:43:15.468Z</t>
         </is>
@@ -1570,99 +1699,112 @@
           <t>Guadalupe Baeza Guerrero</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>5549241783</t>
-        </is>
-      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>5549241783</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
           <t>fotos/isidro_diaz_cruz/device-1mw0yj/BAGG491223MDFZRD04_frontal.jpg</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/GeomaticaAO/APP_PAPEAO_MGE/main/fotos/isidro_diaz_cruz/device-1mw0yj/BAGG491223MDFZRD04_frontal.jpg</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
         <is>
           <t>fotos/isidro_diaz_cruz/device-1mw0yj/BAGG491223MDFZRD04_reverso.jpg</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/GeomaticaAO/APP_PAPEAO_MGE/main/fotos/isidro_diaz_cruz/device-1mw0yj/BAGG491223MDFZRD04_reverso.jpg</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
         <is>
           <t>fotos/isidro_diaz_cruz/device-1mw0yj/BAGG491223MDFZRD04_comprobante.jpg</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/GeomaticaAO/APP_PAPEAO_MGE/main/fotos/isidro_diaz_cruz/device-1mw0yj/BAGG491223MDFZRD04_comprobante.jpg</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
         <is>
           <t>Callejón Allende</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr">
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr">
         <is>
           <t>12216013</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>BAGG491223MDFZRD04</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>La Mora Santa Lucía</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>01500</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="Z10" t="inlineStr">
         <is>
           <t>Casa amarilla puerta roja justo en la esquina que entre Allende y Av San Isidro</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>19.357095,-99.249925</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>19.357095</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>-99.249925</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
         <is>
           <t>Calle: callejon allende  a num int: 1 Col: Pueblo Santa Lucia</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>2026-03-10T19:45:13.689Z</t>
         </is>
